--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="131">
   <si>
     <t>ID</t>
   </si>
@@ -407,6 +407,27 @@
   </si>
   <si>
     <t>极·朱雀化身</t>
+  </si>
+  <si>
+    <t>极·玄武</t>
+  </si>
+  <si>
+    <t>1E+230</t>
+  </si>
+  <si>
+    <t>1E+220</t>
+  </si>
+  <si>
+    <t>极·玄武幻象</t>
+  </si>
+  <si>
+    <t>极·玄武分身</t>
+  </si>
+  <si>
+    <t>极·玄武法相</t>
+  </si>
+  <si>
+    <t>极·玄武化身</t>
   </si>
 </sst>
 </file>
@@ -1396,7 +1417,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AE52"/>
+  <dimension ref="C1:AE59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
@@ -5304,6 +5325,457 @@
         <v>89</v>
       </c>
     </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C54" s="2">
+        <v>41</v>
+      </c>
+      <c r="D54" s="2">
+        <v>9</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G54" s="1">
+        <v>100</v>
+      </c>
+      <c r="H54" s="1">
+        <v>400</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J54" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="K54" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L54" s="8">
+        <v>1</v>
+      </c>
+      <c r="M54" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N54" s="8">
+        <v>3</v>
+      </c>
+      <c r="O54" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="P54" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q54" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="R54" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S54" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="T54" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="U54" s="2">
+        <v>800000</v>
+      </c>
+      <c r="V54" s="2">
+        <v>800000</v>
+      </c>
+      <c r="W54" s="2">
+        <v>800000</v>
+      </c>
+      <c r="X54" s="2">
+        <v>800000</v>
+      </c>
+      <c r="Y54" s="2">
+        <v>1600</v>
+      </c>
+      <c r="Z54" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA54" s="2">
+        <v>700</v>
+      </c>
+      <c r="AB54" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC54" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD54" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE54" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C55" s="2">
+        <v>42</v>
+      </c>
+      <c r="D55" s="2">
+        <v>9</v>
+      </c>
+      <c r="E55" s="1">
+        <v>2</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G55" s="1">
+        <v>90</v>
+      </c>
+      <c r="H55" s="1">
+        <v>400</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J55" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="K55" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L55" s="8">
+        <v>1</v>
+      </c>
+      <c r="M55" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N55" s="8">
+        <v>3</v>
+      </c>
+      <c r="O55" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="P55" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q55" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="R55" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S55" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="T55" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="U55" s="2">
+        <v>800000</v>
+      </c>
+      <c r="V55" s="2">
+        <v>800000</v>
+      </c>
+      <c r="W55" s="2">
+        <v>800000</v>
+      </c>
+      <c r="X55" s="2">
+        <v>800000</v>
+      </c>
+      <c r="Y55" s="2">
+        <v>1600</v>
+      </c>
+      <c r="Z55" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA55" s="2">
+        <v>700</v>
+      </c>
+      <c r="AB55" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC55" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD55" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE55" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C56" s="2">
+        <v>43</v>
+      </c>
+      <c r="D56" s="2">
+        <v>9</v>
+      </c>
+      <c r="E56" s="1">
+        <v>3</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G56" s="1">
+        <v>80</v>
+      </c>
+      <c r="H56" s="1">
+        <v>400</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J56" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="K56" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L56" s="8">
+        <v>1</v>
+      </c>
+      <c r="M56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N56" s="8">
+        <v>3</v>
+      </c>
+      <c r="O56" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="P56" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q56" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="R56" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S56" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="T56" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="U56" s="2">
+        <v>800000</v>
+      </c>
+      <c r="V56" s="2">
+        <v>800000</v>
+      </c>
+      <c r="W56" s="2">
+        <v>800000</v>
+      </c>
+      <c r="X56" s="2">
+        <v>800000</v>
+      </c>
+      <c r="Y56" s="2">
+        <v>1600</v>
+      </c>
+      <c r="Z56" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="2">
+        <v>700</v>
+      </c>
+      <c r="AB56" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD56" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE56" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C57" s="2">
+        <v>44</v>
+      </c>
+      <c r="D57" s="2">
+        <v>9</v>
+      </c>
+      <c r="E57" s="1">
+        <v>4</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G57" s="1">
+        <v>70</v>
+      </c>
+      <c r="H57" s="1">
+        <v>400</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J57" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L57" s="8">
+        <v>1</v>
+      </c>
+      <c r="M57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N57" s="8">
+        <v>3</v>
+      </c>
+      <c r="O57" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="P57" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="R57" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S57" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="T57" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="U57" s="2">
+        <v>800000</v>
+      </c>
+      <c r="V57" s="2">
+        <v>800000</v>
+      </c>
+      <c r="W57" s="2">
+        <v>800000</v>
+      </c>
+      <c r="X57" s="2">
+        <v>800000</v>
+      </c>
+      <c r="Y57" s="2">
+        <v>1600</v>
+      </c>
+      <c r="Z57" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="2">
+        <v>700</v>
+      </c>
+      <c r="AB57" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD57" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE57" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C58" s="2">
+        <v>45</v>
+      </c>
+      <c r="D58" s="2">
+        <v>9</v>
+      </c>
+      <c r="E58" s="2">
+        <v>5</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G58" s="2">
+        <v>60</v>
+      </c>
+      <c r="H58" s="1">
+        <v>400</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J58" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="K58" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L58" s="8">
+        <v>1</v>
+      </c>
+      <c r="M58" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N58" s="8">
+        <v>3</v>
+      </c>
+      <c r="O58" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="P58" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="R58" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S58" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="T58" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="U58" s="2">
+        <v>800000</v>
+      </c>
+      <c r="V58" s="2">
+        <v>800000</v>
+      </c>
+      <c r="W58" s="2">
+        <v>800000</v>
+      </c>
+      <c r="X58" s="2">
+        <v>800000</v>
+      </c>
+      <c r="Y58" s="2">
+        <v>1600</v>
+      </c>
+      <c r="Z58" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA58" s="2">
+        <v>700</v>
+      </c>
+      <c r="AB58" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD58" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE58" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:31">
+      <c r="U59" s="2"/>
+      <c r="V59" s="2"/>
+      <c r="W59" s="2"/>
+      <c r="X59" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AE5" errorStyle="warning">
